--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1530" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="273">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -429,6 +429,119 @@
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.header.status.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.header.status.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.header.status.coding</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.header.status.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>fr-lm-laboratory-observation.header.status.directSubject[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patient
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedure</t>
+  </si>
+  <si>
+    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
+  </si>
+  <si>
+    <t>fr-lm-observation.header.status.directSubject[x]</t>
   </si>
   <si>
     <t>fr-lm-laboratory-observation.header.source</t>
@@ -451,19 +564,6 @@
     <t>fr-lm-entry.header.language</t>
   </si>
   <si>
-    <t>fr-lm-laboratory-observation.directSubject[x]</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-patient
-https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-devicehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-health-professionalhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-organisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-procedure</t>
-  </si>
-  <si>
-    <t>Sujet direct de l'observation si différent du patient, par exemple dans le cas d’une observation portant sur un dispositif implanté. D’autres types de sujets peuvent être autorisés selon les implémentations.</t>
-  </si>
-  <si>
-    <t>fr-lm-observation.directSubject[x]</t>
-  </si>
-  <si>
     <t>fr-lm-laboratory-observation.observationDate[x]</t>
   </si>
   <si>
@@ -490,10 +590,6 @@
   </si>
   <si>
     <t>fr-lm-laboratory-observation.originalName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Nom de l'observation</t>
@@ -1069,13 +1165,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ48"/>
+  <dimension ref="A1:AJ52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.51171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="59.51171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -1086,7 +1182,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="196.6875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -1100,7 +1196,7 @@
     <col min="26" max="26" width="80.01171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -2847,13 +2943,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2904,7 +3000,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2921,21 +3017,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>73</v>
@@ -2947,15 +3043,17 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>73</v>
@@ -2992,39 +3090,39 @@
         <v>73</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>73</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3035,7 +3133,7 @@
         <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>73</v>
@@ -3044,19 +3142,23 @@
         <v>73</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>155</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>73</v>
       </c>
@@ -3104,27 +3206,27 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3132,7 +3234,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -3144,19 +3246,23 @@
         <v>73</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>73</v>
       </c>
@@ -3204,10 +3310,10 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3216,15 +3322,15 @@
         <v>73</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3232,7 +3338,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3247,13 +3353,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>167</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3283,7 +3389,7 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
@@ -3304,10 +3410,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3321,10 +3427,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3347,13 +3453,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3404,7 +3510,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3421,10 +3527,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3450,10 +3556,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3504,7 +3610,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3521,10 +3627,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3532,7 +3638,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3547,13 +3653,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3604,10 +3710,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3621,10 +3727,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3632,7 +3738,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3647,13 +3753,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3683,7 +3789,7 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -3704,10 +3810,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3721,10 +3827,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3747,13 +3853,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3804,7 +3910,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3821,10 +3927,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3832,7 +3938,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>79</v>
@@ -3847,13 +3953,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3904,10 +4010,10 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>79</v>
@@ -3921,10 +4027,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3947,13 +4053,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4004,7 +4110,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4021,10 +4127,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4035,7 +4141,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -4047,13 +4153,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4104,13 +4210,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -4121,10 +4227,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4147,13 +4253,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4183,7 +4289,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4204,7 +4310,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4221,10 +4327,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4232,7 +4338,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -4247,13 +4353,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4283,7 +4389,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4304,10 +4410,10 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4321,10 +4427,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4347,13 +4453,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>131</v>
+        <v>207</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4383,7 +4489,7 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="Z33" t="s" s="2">
         <v>73</v>
@@ -4404,7 +4510,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4421,10 +4527,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4435,7 +4541,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4447,13 +4553,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4483,7 +4589,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4504,13 +4610,13 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
@@ -4521,10 +4627,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4535,7 +4641,7 @@
         <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>73</v>
@@ -4547,13 +4653,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>131</v>
+        <v>214</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4583,7 +4689,7 @@
         <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4604,13 +4710,13 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>73</v>
@@ -4621,10 +4727,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4647,13 +4753,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4683,7 +4789,7 @@
         <v>73</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>73</v>
@@ -4704,7 +4810,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4721,10 +4827,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4747,13 +4853,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4783,7 +4889,7 @@
         <v>73</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>73</v>
+        <v>223</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>73</v>
@@ -4804,7 +4910,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4821,10 +4927,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4835,7 +4941,7 @@
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
@@ -4850,10 +4956,10 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4883,10 +4989,10 @@
         <v>73</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>213</v>
+        <v>73</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>73</v>
@@ -4904,13 +5010,13 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>73</v>
@@ -4921,10 +5027,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4935,7 +5041,7 @@
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -4947,13 +5053,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4983,7 +5089,7 @@
         <v>73</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>73</v>
+        <v>231</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
@@ -5004,13 +5110,13 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>73</v>
@@ -5021,10 +5127,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5035,7 +5141,7 @@
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -5047,13 +5153,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>80</v>
+        <v>234</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5083,7 +5189,7 @@
         <v>73</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>73</v>
+        <v>216</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>73</v>
@@ -5104,13 +5210,13 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>73</v>
@@ -5121,10 +5227,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5135,7 +5241,7 @@
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
@@ -5147,13 +5253,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5204,13 +5310,13 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>73</v>
@@ -5221,10 +5327,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5247,13 +5353,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5283,10 +5389,10 @@
         <v>73</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>73</v>
+        <v>243</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -5304,7 +5410,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5321,10 +5427,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5335,7 +5441,7 @@
         <v>74</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>73</v>
@@ -5347,13 +5453,13 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>226</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5404,13 +5510,13 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>73</v>
@@ -5421,10 +5527,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5435,7 +5541,7 @@
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>73</v>
@@ -5447,13 +5553,13 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5504,13 +5610,13 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>73</v>
@@ -5521,10 +5627,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5535,7 +5641,7 @@
         <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
@@ -5547,13 +5653,13 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>88</v>
+        <v>252</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5604,13 +5710,13 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>73</v>
@@ -5621,10 +5727,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5635,7 +5741,7 @@
         <v>74</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>73</v>
@@ -5647,13 +5753,13 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5704,13 +5810,13 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>73</v>
@@ -5721,10 +5827,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5747,13 +5853,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5804,7 +5910,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -5821,10 +5927,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5847,13 +5953,13 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>236</v>
+        <v>103</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5904,7 +6010,7 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -5916,6 +6022,406 @@
         <v>73</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-laboratory-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="275">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -583,6 +583,9 @@
     <t>Type d'observation</t>
   </si>
   <si>
+    <t>required</t>
+  </si>
+  <si>
     <t>LOINC (2.16.840.1.113883.6.1) ou autre</t>
   </si>
   <si>
@@ -690,6 +693,9 @@
     <t>Limite inférieure de l'intervalle</t>
   </si>
   <si>
+    <t>preferred</t>
+  </si>
+  <si>
     <t>(preferred): UCUM for units</t>
   </si>
   <si>
@@ -769,7 +775,7 @@
     <t>Interprétation</t>
   </si>
   <si>
-    <t>(preferred): HL7 Observation Interpretation Codes</t>
+    <t>HL7 Observation Interpretation Codes</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
@@ -3786,10 +3792,10 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -3810,7 +3816,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3827,10 +3833,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3856,10 +3862,10 @@
         <v>136</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3910,7 +3916,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3927,10 +3933,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3956,10 +3962,10 @@
         <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4010,7 +4016,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -4027,10 +4033,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4053,13 +4059,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4110,7 +4116,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -4127,10 +4133,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4153,13 +4159,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4210,7 +4216,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4227,10 +4233,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4253,13 +4259,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4310,7 +4316,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4327,10 +4333,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4356,10 +4362,10 @@
         <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4410,7 +4416,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4427,10 +4433,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4453,13 +4459,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4510,7 +4516,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4527,10 +4533,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4556,10 +4562,10 @@
         <v>80</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4610,7 +4616,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4627,10 +4633,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4653,13 +4659,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4686,10 +4692,10 @@
         <v>73</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4710,7 +4716,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4727,10 +4733,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4753,13 +4759,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4786,10 +4792,10 @@
         <v>73</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>73</v>
@@ -4810,7 +4816,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4827,10 +4833,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4856,10 +4862,10 @@
         <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4886,10 +4892,10 @@
         <v>73</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Z37" t="s" s="2">
         <v>73</v>
@@ -4910,7 +4916,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4927,10 +4933,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4956,10 +4962,10 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4986,10 +4992,10 @@
         <v>73</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Z38" t="s" s="2">
         <v>73</v>
@@ -5010,7 +5016,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -5027,10 +5033,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5056,10 +5062,10 @@
         <v>131</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5086,10 +5092,10 @@
         <v>73</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
@@ -5110,7 +5116,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -5127,10 +5133,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5153,13 +5159,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5186,10 +5192,10 @@
         <v>73</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>73</v>
+        <v>217</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>73</v>
@@ -5210,7 +5216,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5227,10 +5233,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5256,10 +5262,10 @@
         <v>136</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5310,7 +5316,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5327,10 +5333,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5356,10 +5362,10 @@
         <v>131</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5386,13 +5392,13 @@
         <v>73</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>73</v>
@@ -5410,7 +5416,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5427,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5456,10 +5462,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5510,7 +5516,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -5527,10 +5533,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5556,10 +5562,10 @@
         <v>80</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5610,7 +5616,7 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -5627,10 +5633,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5653,13 +5659,13 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5710,7 +5716,7 @@
         <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -5727,10 +5733,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5753,13 +5759,13 @@
         <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5810,7 +5816,7 @@
         <v>73</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -5827,10 +5833,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5853,13 +5859,13 @@
         <v>73</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5910,7 +5916,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -5927,10 +5933,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5956,10 +5962,10 @@
         <v>103</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6010,7 +6016,7 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
@@ -6027,10 +6033,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6056,10 +6062,10 @@
         <v>88</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6110,7 +6116,7 @@
         <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -6127,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6153,13 +6159,13 @@
         <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6210,7 +6216,7 @@
         <v>73</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -6227,10 +6233,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6253,13 +6259,13 @@
         <v>73</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6310,7 +6316,7 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -6327,10 +6333,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6353,13 +6359,13 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6410,7 +6416,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
